--- a/www/download/COUNTRY.PRT.zdW16.xlsx
+++ b/www/download/COUNTRY.PRT.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.0827070735622</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.1165596972807</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.05753457754142</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.883981997217767</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.803913137718776</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.803781222414648</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.796427482545589</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.729647362252598</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.679896297989307</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.7169636660439</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.754330494738976</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.718380451505892</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.77836230920116</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.752941621034942</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752715091116079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5.042</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>5.064</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5.041</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>5.061</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5.062</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.942</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.871</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.777</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.581</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.545</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.029</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.091</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.133</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.088</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4.102</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>4.103</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.142</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.167</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.191</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.092</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.066</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.985</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.795</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.711</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.794</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9642.583</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9761.2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>9745.748</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>9632.705</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>9591.538</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9540.612</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>9542.568</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>9552.257</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>9517.419</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>9287.535</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>9196.015</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8913.526</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8477.996</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8310.859</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8496.028</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7613.067</t>
+          <t>12680045252.954</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7690.033</t>
+          <t>12535434086.3387</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7744.403</t>
+          <t>12221670546.1304</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7647.665</t>
+          <t>12062810220.6729</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7699.433</t>
+          <t>12441198068.5348</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7709.024</t>
+          <t>11722742375.8453</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7764.62</t>
+          <t>11663695820.7522</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7829.745</t>
+          <t>11721112317.5624</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7838.12</t>
+          <t>11786463544.5444</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7679.032</t>
+          <t>10086534840.6854</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7667.207</t>
+          <t>9970525975.96004</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7416.264</t>
+          <t>10447106944.5326</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7013.685</t>
+          <t>9591734525.50566</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6909.289</t>
+          <t>9708865456.96416</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7069.171</t>
+          <t>9877415532.93961</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3456511041.22145</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3567080703.40906</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3455446463.04891</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3544885477.07974</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3603911501.57679</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3529165180.61434</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3368737982.1922</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3280686072.2708</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3317345872.41792</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2983889996.84319</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2848172668.98791</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2891693529.44417</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2660232743.58568</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2667183851.0964</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2625775001.22659</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2589993.10756368</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2559871.92149019</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2311833.7220219</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1933531.04857237</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1789628.07664198</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1635517.89585989</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1561173.16885175</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1353509.29780559</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1225712.03753756</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1246319.71981347</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1210795.82462898</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1182063.42518557</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1218331.48909425</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1182054.5445134</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1202553.50430625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>52365.0465021402</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>51551.6721377962</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>51317.8532905595</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>54449.8861638407</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>58421.5547570116</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>61614.8622889407</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>64291.4056746602</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>71435.5350398787</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>76294.8368259277</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>67056.995545616</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>72576.9115980994</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>75136.5225262572</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>69509.4365947807</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>67702.965609886</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>69003.9463222465</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>115024.999032304</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>112048.111509437</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>110047.097722858</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>118251.024501977</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>134402.778052943</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>136783.129518074</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>143812.315515546</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>162118.217713726</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>177802.01064277</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>139056.641667356</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>151866.490876744</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>169663.312617242</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>152160.306514897</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>153125.382656662</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>156327.551638769</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.20252934511377</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.15583375858321</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.2412163183008</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.15737999138412</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.13641011901411</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.18437607917747</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.30490469755893</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.38661817300321</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.36276840023528</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.57349701501196</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.69197407990174</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.56467842269078</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.63649299743089</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.59048096634201</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.69222267585675</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827070735622</t>
+          <t>857.980331232085</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165596972807</t>
+          <t>871.978445094727</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05753457754142</t>
+          <t>836.09085791653</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.883981997217767</t>
+          <t>867.086928475796</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803913137718776</t>
+          <t>878.53139817093</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803781222414648</t>
+          <t>860.086024223203</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796427482545589</t>
+          <t>813.382617077341</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729647362252598</t>
+          <t>787.373475927921</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679896297989307</t>
+          <t>791.570633194757</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.7169636660439</t>
+          <t>729.256125670125</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.754330494738976</t>
+          <t>700.438649914519</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718380451505892</t>
+          <t>725.582642746709</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.77836230920116</t>
+          <t>700.917104987584</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.752941621034942</t>
+          <t>718.70245050575</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752715091116079</t>
+          <t>692.12814725895</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>186987570.50575</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>196620014.614191</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>127004719.863092</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>339953714.586893</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>487824685.551247</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>377592272.101124</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>596815947.19986</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>944557775.257867</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>946403931.500245</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>550365821.041889</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>587450622.190849</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1196295601.2053</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1469085158.1953</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1647422599.39232</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1570829153.73212</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>234911195.194863</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>228580149.281793</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>67965579.7059995</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>187970153.281694</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>244920245.186527</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>139711530.711311</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>264405327.657017</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>487093862.650621</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>481771199.255192</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>129115517.465634</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>369182696.038633</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>943927212.159726</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1209573268.43132</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1328449853.79149</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1184933271.59386</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-47923624.6891127</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>-31960134.6676015</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>59039140.1570926</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>151983561.305199</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>242904440.36472</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>237880741.389813</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>332410619.542843</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>457463912.607246</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>464632732.245054</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>421250303.576255</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>218267926.152216</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>252368389.045577</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>259511889.763982</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>318972745.600836</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>385895882.138264</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1889.7268570691</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>1879.84056869211</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1873.86047434464</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1870.6359902844</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>1876.90336892399</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>1878.75133734802</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>1874.76941501434</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>1879.15984659028</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>1870.29807866681</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>1876.73846259125</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>1885.56269013125</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>1860.88614773144</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>1847.9630390793</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1861.78501849851</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>1863.36309264926</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1912.48985706387</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1902.71242135943</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>1892.38563902708</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1888.68789184593</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1893.97747278818</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1892.62559498577</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1885.52909002765</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>1887.17864895632</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1873.45973546761</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1879.42484688646</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1887.76777331651</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1866.0114298085</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1850.50891752327</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>1867.52491486867</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>1869.12812609884</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>22117.8840935693</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22029.0958347143</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>24891.9781814064</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>32494.3477920757</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>39716.4617514861</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>40660.7523554102</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>49438.9144542964</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>61369.9044427748</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>68684.4658898986</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>54157.1619454205</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>58470.2101637274</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>69473.7189091155</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>66506.6884918643</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>73582.124482093</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>76632.9618501228</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1455828158.02919</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1455217455.02502</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1461557494.03784</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1595676705.88762</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1777731646.79272</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1612691357.02122</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1868523426.27498</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1968037161.35326</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2006814721.87375</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1538096181.47491</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1663478642.1158</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1991760501.70309</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2032538570.15971</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2257242369.89642</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2339688426.76905</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>42357.5264942352</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>41757.6192782508</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>43340.6308948475</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>50671.3932661751</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>61409.584044034</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>64477.2705479335</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>72424.3517965141</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>83868.1986098413</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>96932.6756713827</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>75234.6877172924</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>80957.7324499845</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>86553.9960365157</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>75052.0217685794</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>79030.4539770958</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>83276.0082955492</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9642.583</t>
+          <t>4410685793.99997</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9761.2</t>
+          <t>4459815469.67671</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9745.748</t>
+          <t>4230935760.70707</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9632.705</t>
+          <t>4389709091.07455</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9591.538</t>
+          <t>4934327494.53047</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9540.612</t>
+          <t>4647710920.36552</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9542.568</t>
+          <t>4792933037.28936</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9552.257</t>
+          <t>4866154177.72412</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9517.419</t>
+          <t>5094681557.18912</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9287.535</t>
+          <t>3883249384.9301</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>9196.015</t>
+          <t>3957900948.7443</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8913.526</t>
+          <t>4415458047.43505</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8477.996</t>
+          <t>4119788793.18775</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8310.859</t>
+          <t>4302724039.71724</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8496.028</t>
+          <t>4391202238.9622</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7613.067</t>
+          <t>-20239.6424006658</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7690.033</t>
+          <t>-19728.5234435364</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7744.403</t>
+          <t>-18448.6527134411</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7647.665</t>
+          <t>-18177.0454740994</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7699.433</t>
+          <t>-21693.1222925479</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7709.024</t>
+          <t>-23816.5181925233</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7764.62</t>
+          <t>-22985.4373422178</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7829.745</t>
+          <t>-22498.2941670665</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7838.12</t>
+          <t>-28248.2097814841</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7679.032</t>
+          <t>-21077.5257718719</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7667.207</t>
+          <t>-22487.5222862571</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7416.264</t>
+          <t>-17080.2771274002</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7013.685</t>
+          <t>-8545.33327671506</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>6909.289</t>
+          <t>-5448.32949500282</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7069.171</t>
+          <t>-6643.04644542634</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14026.61</t>
+          <t>-2954857635.97078</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13831.187</t>
+          <t>-3004598014.6517</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13516.389</t>
+          <t>-2769378266.66923</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13404.107</t>
+          <t>-2794032385.18693</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13832.174</t>
+          <t>-3156595847.73775</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13074.048</t>
+          <t>-3035019563.3443</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13124.006</t>
+          <t>-2924409611.01438</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13210.415</t>
+          <t>-2898117016.37086</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13418.515</t>
+          <t>-3087866835.31537</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11542.177</t>
+          <t>-2345153203.45519</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11403.49</t>
+          <t>-2294422306.6285</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12027.679</t>
+          <t>-2423697545.73196</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>11144.634</t>
+          <t>-2087250223.02804</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>11211.214</t>
+          <t>-2045481669.82083</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>9877.416</t>
+          <t>-2051513812.19315</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>47282.87076</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>48501.0983786871</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>53002.5316846742</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>63724.3694463865</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>72621.99175</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>73705.289651899</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>76555.8029076955</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>87181.6165</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>93572.1798509901</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>87355.0082681331</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>85333.6023000955</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>84785.2343186652</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>73527.0939037566</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>77531.6396415921</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>78117.0533862634</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5772.581</t>
+          <t>0.137485767881677</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5767.367</t>
+          <t>0.136602262694524</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5699.286</t>
+          <t>0.134668158958445</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5554.444</t>
+          <t>0.132124305872123</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5407.88</t>
+          <t>0.133500935777477</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5280.587</t>
+          <t>0.128635032851367</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5214.264</t>
+          <t>0.11766234494795</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5164.774</t>
+          <t>0.121058685573246</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5057.571</t>
+          <t>0.11210729717678</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4864.009</t>
+          <t>0.109879119208197</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4764.909</t>
+          <t>0.110192404489018</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4626.571</t>
+          <t>0.106155630313937</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4381.669</t>
+          <t>0.107049340971579</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>4292.685</t>
+          <t>0.11068891832957</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4359.952</t>
+          <t>0.111014654350327</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>57101.8660596002</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>58575.3300254107</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>64705.2311535452</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>79341.5406414</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>89973.1302613357</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>94223.31582802</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>97739.4729861959</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>111048.697915458</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>123016.626414371</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>116640.377253932</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>112474.288475428</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>113611.638066717</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>96751.2161769926</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>101307.715193514</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>101288.661961636</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3849.499</t>
+          <t>66573.742782602</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3943.755</t>
+          <t>68274.6563741539</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3847.008</t>
+          <t>74853.6401083371</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3960.701</t>
+          <t>91779.3008224205</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4017.096</t>
+          <t>103325.112915802</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3941.184</t>
+          <t>107866.063845997</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3777.037</t>
+          <t>111386.143639843</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3670.828</t>
+          <t>126438.328653965</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3732.273</t>
+          <t>139891.449500806</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3378.896</t>
+          <t>132083.530151212</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3217.864</t>
+          <t>126748.879554182</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3276.147</t>
+          <t>128332.394980546</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3018.827</t>
+          <t>109819.83543509</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3009.971</t>
+          <t>114198.453209169</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2625.775</t>
+          <t>114218.832658478</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>271986.310390906</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>94.99</t>
+          <t>281336.713412227</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>101.31</t>
+          <t>320423.494078458</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>399704.797574366</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>467782.789090641</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>492256.72487889</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>105.57</t>
+          <t>585505.987160937</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>113.3</t>
+          <t>678425.465774138</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>110.01</t>
+          <t>799044.275191761</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>127.26</t>
+          <t>771899.208122596</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>754527.396850811</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>126.37</t>
+          <t>813659.141830659</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>132.33</t>
+          <t>742730.741974841</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>129.55</t>
+          <t>765300.457405339</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>169.22</t>
+          <t>786213.11316623</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>86440.6286926312</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>87655.9572948331</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>87614.8175230225</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.233</t>
+          <t>86816.9815211656</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.061</t>
+          <t>86773.0661461693</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>88226.9165300804</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>88128.3060764457</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>89353.1833733359</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>90082.5818844948</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>87174.1565703615</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>88304.7414114484</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>86849.2998893825</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>82757.7821165752</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>81203.5689853983</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>80889.9502256556</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>75269.3351087847</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>76349.395153264</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76488.509978508</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>75847.360744102</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>76171.3000353374</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>77514.2856966523</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>77706.0015616555</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>78733.3924695258</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>79280.6351713698</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>76973.7673938506</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>78359.7021408815</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>76490.5256707825</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>72758.1165384852</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>72055.3747578817</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>71711.0418037964</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>37394.246737398</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>38431.2316311511</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>43150.8420345782</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>52810.7189332704</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>62449.4400841985</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>63321.4599761023</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>68892.00743042</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>82129.2951460345</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>89578.6940163271</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>84815.6051060159</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>83143.1881118303</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>86374.4990617305</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>79508.8364477386</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>84710.279827322</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>87281.1770038436</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7613067000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7690033000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7744403000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7647665000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7699433000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7709024000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7764620000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7829745000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7838120000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7679032000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7667207000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7416264000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7013685000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6909289000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7069171000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9642582610.33032</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9761200128.4371</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9745748193.27666</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9632704872.87154</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9591537537.01811</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9540612066.78759</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9542568448.17543</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>9552256680.27624</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9517419005.94107</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9287534971.61034</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9196015297.90082</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8913526077.68065</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8477995575.09781</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8310859376.14855</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8496028440.77597</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5772581307.59647</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5767367065.97202</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5699286115.03581</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5554443575.41843</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5407880288.88379</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5280586572.92968</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5214264139.96345</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5164773838.96558</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5057571113.14379</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4864008750.48118</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4764908823.31054</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4626570554.13595</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4381668768.32186</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4292684679.31078</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4359952190.72091</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5041900</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5130150</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5149980</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5100210</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5064230</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5040940</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5060950</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5061660</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5080130</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4941690</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4871370</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4776780</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4581440</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4450200</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4545450</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4028660</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4090790</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4132860</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4088270</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4102200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103270</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4141640</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4166620</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4190840</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4091690</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4066270</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3985340</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3795360</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3711110</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3793770</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9642582610.33032</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9761200128.4371</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9745748193.27666</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9632704872.87154</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9591537537.01811</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9540612066.78759</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9542568448.17543</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>9552256680.27624</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>9517419005.94107</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9287534971.61034</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9196015297.90082</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8913526077.68065</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8477995575.09781</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8310859376.14855</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8496028440.77597</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7613067000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7690033000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7744403000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7647665000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7699433000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7709024000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7764620000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7829745000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7838120000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7679032000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7667207000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7416264000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7013685000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6909289000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7069171000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>226473.00048</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>232029.972363258</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>250750.41054124</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>303967.118019651</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>351427.49873</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>365509.673558174</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>384162.453956551</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>444873.8935</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>496893.911699466</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>444009.495613162</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>435458.424624214</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>454933.089718619</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>397564.147927618</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>408870.452606089</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>414280.893686788</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>103967.98952</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>106706.156683258</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>118004.43486124</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>144589.408899651</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>165774.553</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>171187.722878174</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>180278.000396551</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>208567.6238</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>229469.525779466</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>216899.232893162</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>209892.293034214</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>214706.601718619</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>189329.288567618</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>198908.068976089</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>201499.850158618</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>373228.013791767</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>388087.806478108</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>404825.851284165</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>407342.899832548</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>418567.597508081</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>422163.197233242</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>482507.286886443</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>493606.798444216</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>515800.016051546</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>523613.658113809</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>525668.886372709</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>534445.209158318</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>527014.280088295</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>515622.775857139</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>522799.011135463</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
